--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Value of KPI</t>
         </is>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feasibility" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KPIs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Value of KPI</t>
+          <t>KPI-value</t>
         </is>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,30 +578,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>total_waiting_time_min</t>
+          <t>total_material_trips</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>775</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>total_waiting_time_hours</t>
+          <t>total_waiting_time_min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.91666666666667</v>
+        <v>775</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>total_waiting_time_hours</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12.91666666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>avg_waiting_time_per_bus_min</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>38.75</v>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,35 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280755D0-8274-4C19-9EDF-9DCD78D4D282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
+    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Errors</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Location of end of trip and new trip match</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>No Bus Overlap</t>
+  </si>
+  <si>
+    <t>Required Trips of lines 400 and 401 included in bus plan</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Charging Duration is at least 15 min</t>
+  </si>
+  <si>
+    <t>Number of Charging Speeds is equal to 2</t>
+  </si>
+  <si>
+    <t>Battery Capacity at least 10%</t>
+  </si>
+  <si>
+    <t>Overall status bus plan</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>KPI-value</t>
+  </si>
+  <si>
+    <t>total_energy_kwh</t>
+  </si>
+  <si>
+    <t>total_distance_m</t>
+  </si>
+  <si>
+    <t>total_distance_km</t>
+  </si>
+  <si>
+    <t>deployed_buses_count</t>
+  </si>
+  <si>
+    <t>total_material_trips</t>
+  </si>
+  <si>
+    <t>total_waiting_time_min</t>
+  </si>
+  <si>
+    <t>total_waiting_time_hours</t>
+  </si>
+  <si>
+    <t>avg_waiting_time_per_bus_min</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,80 +126,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,104 +428,99 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Location of end of trip and new trip match</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
         <v>18</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bus Overlap</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Required Trips included in plan</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Charging Duration is at least 15 min</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
         <v>106</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Battery Capacity at least 10%</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>130</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -515,103 +529,79 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>KPI-value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>total_energy_kwh</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6537.540400000004</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>total_distance_m</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>6537.5404000000044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
         <v>3533117</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>total_distance_km</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3533.117</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>deployed_buses_count</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>3533.1170000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
         <v>20</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>total_material_trips</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
         <v>251</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>total_waiting_time_min</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
         <v>775</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>total_waiting_time_hours</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8">
         <v>12.91666666666667</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>avg_waiting_time_per_bus_min</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9">
         <v>38.75</v>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280755D0-8274-4C19-9EDF-9DCD78D4D282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5CA002-668F-4747-9927-C7D45171B19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Check</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Number of Charging Speeds is equal to 2</t>
+  </si>
+  <si>
+    <t>Assumed SOH percentage between 85% and 95%</t>
   </si>
   <si>
     <t>Battery Capacity at least 10%</t>
@@ -429,10 +432,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="39.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -517,10 +520,21 @@
         <v>11</v>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
         <v>130</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
+      <c r="C9" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -535,15 +549,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>6537.5404000000044</v>
@@ -551,7 +565,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>3533117</v>
@@ -559,7 +573,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>3533.1170000000002</v>
@@ -567,7 +581,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -575,7 +589,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>251</v>
@@ -583,7 +597,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>775</v>
@@ -591,7 +605,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>12.91666666666667</v>
@@ -599,7 +613,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>38.75</v>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5CA002-668F-4747-9927-C7D45171B19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD457A8-F274-47EC-9833-1BCF3A341834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>Check</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Number of Charging Speeds is equal to 2</t>
+  </si>
+  <si>
+    <t>Charging speeds configured (Quick: 7.50 kWh/min, Slow: 1.00 kWh/min)</t>
   </si>
   <si>
     <t>Assumed SOH percentage between 85% and 95%</t>
@@ -432,10 +435,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.21875" customWidth="1"/>
+    <col min="1" max="1" width="65.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -531,10 +534,21 @@
         <v>12</v>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
         <v>130</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
+      <c r="C10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -546,18 +560,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>6537.5404000000044</v>
@@ -565,7 +582,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>3533117</v>
@@ -573,7 +590,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>3533.1170000000002</v>
@@ -581,7 +598,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -589,7 +606,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>251</v>
@@ -597,7 +614,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>775</v>
@@ -605,7 +622,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>12.91666666666667</v>
@@ -613,7 +630,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>38.75</v>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD457A8-F274-47EC-9833-1BCF3A341834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B0D102-C8B7-42F5-8916-3D4358EEA4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
     <t>Number of Charging Speeds is equal to 2</t>
   </si>
   <si>
-    <t>Charging speeds configured (Quick: 7.50 kWh/min, Slow: 1.00 kWh/min)</t>
+    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
   </si>
   <si>
     <t>Assumed SOH percentage between 85% and 95%</t>
@@ -438,7 +438,7 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="65.109375" customWidth="1"/>
+    <col min="1" max="1" width="75.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -560,9 +560,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,119 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B0D102-C8B7-42F5-8916-3D4358EEA4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
-    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
+    <sheet name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Errors</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Location of end of trip and new trip match</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>No Bus Overlap</t>
-  </si>
-  <si>
-    <t>Required Trips of lines 400 and 401 included in bus plan</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Charging Duration is at least 15 min</t>
-  </si>
-  <si>
-    <t>Number of Charging Speeds is equal to 2</t>
-  </si>
-  <si>
-    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
-  </si>
-  <si>
-    <t>Assumed SOH percentage between 85% and 95%</t>
-  </si>
-  <si>
-    <t>Battery Capacity at least 10%</t>
-  </si>
-  <si>
-    <t>Overall status bus plan</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>KPI</t>
-  </si>
-  <si>
-    <t>KPI-value</t>
-  </si>
-  <si>
-    <t>total_energy_kwh</t>
-  </si>
-  <si>
-    <t>total_distance_m</t>
-  </si>
-  <si>
-    <t>total_distance_km</t>
-  </si>
-  <si>
-    <t>deployed_buses_count</t>
-  </si>
-  <si>
-    <t>total_material_trips</t>
-  </si>
-  <si>
-    <t>total_waiting_time_min</t>
-  </si>
-  <si>
-    <t>total_waiting_time_hours</t>
-  </si>
-  <si>
-    <t>avg_waiting_time_per_bus_min</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -132,21 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -434,121 +409,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="75.88671875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Location of end of trip and new trip match</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No Bus Overlap</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Required Trips of lines 400 and 401 included in bus plan</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Charging Duration is at least 15 min</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Number of Charging Speeds is equal to 2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>106</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>0</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Assumed SOH percentage between 85% and 95%</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Battery Capacity at least 10%</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Overall status bus plan</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>130</v>
       </c>
-      <c r="C10" t="s">
-        <v>14</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -557,79 +575,103 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
-        <v>6537.5404000000044</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>KPI-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total_energy_kwh</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6537.540400000004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>total_distance_m</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>3533117</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>3533.1170000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total_distance_km</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3533.117</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>deployed_buses_count</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>20</v>
       </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_material_trips</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>total_waiting_time_min</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>775</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_waiting_time_hours</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>12.91666666666667</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>avg_waiting_time_per_bus_min</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>38.75</v>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,35 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76E0CEA-2872-46E0-8C17-A534795A5A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
+    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Errors</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Location of end of trip and new trip match</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>No Bus Overlap</t>
+  </si>
+  <si>
+    <t>Required Trips of lines 400 and 401 included in bus plan</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Charging Duration is at least 15 min</t>
+  </si>
+  <si>
+    <t>Number of Charging Speeds is equal to 2</t>
+  </si>
+  <si>
+    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
+  </si>
+  <si>
+    <t>Assumed SOH percentage between 85% and 95%</t>
+  </si>
+  <si>
+    <t>Battery Capacity at least 10%</t>
+  </si>
+  <si>
+    <t>Overall status bus plan</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>KPI-value</t>
+  </si>
+  <si>
+    <t>total_energy_kwh</t>
+  </si>
+  <si>
+    <t>total_distance_m</t>
+  </si>
+  <si>
+    <t>total_distance_km</t>
+  </si>
+  <si>
+    <t>deployed_buses_count</t>
+  </si>
+  <si>
+    <t>total_material_trips</t>
+  </si>
+  <si>
+    <t>total_waiting_time_min</t>
+  </si>
+  <si>
+    <t>total_waiting_time_hours</t>
+  </si>
+  <si>
+    <t>avg_waiting_time_per_bus_min</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,80 +132,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,164 +434,121 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="134.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Location of end of trip and new trip match</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
         <v>18</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>No Bus Overlap</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Required Trips of lines 400 and 401 included in bus plan</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Charging Duration is at least 15 min</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
         <v>106</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Number of Charging Speeds is equal to 2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Assumed SOH percentage between 85% and 95%</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Battery Capacity at least 10%</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
         <v>0</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Overall status bus plan</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
         <v>130</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
+      <c r="C10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -575,103 +557,82 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>KPI-value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>total_energy_kwh</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6537.540400000004</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>total_distance_m</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>6537.5404000000044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>3533117</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>total_distance_km</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3533.117</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>deployed_buses_count</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>3533.1170000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>total_material_trips</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>251</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>total_waiting_time_min</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>775</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>total_waiting_time_hours</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
         <v>12.91666666666667</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>avg_waiting_time_per_bus_min</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>38.75</v>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76E0CEA-2872-46E0-8C17-A534795A5A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0150EB28-2E85-4F70-86D8-BE1A87E00F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,125 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0150EB28-2E85-4F70-86D8-BE1A87E00F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
-    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Errors</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Location of end of trip and new trip match</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>No Bus Overlap</t>
-  </si>
-  <si>
-    <t>Required Trips of lines 400 and 401 included in bus plan</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Charging Duration is at least 15 min</t>
-  </si>
-  <si>
-    <t>Number of Charging Speeds is equal to 2</t>
-  </si>
-  <si>
-    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
-  </si>
-  <si>
-    <t>Assumed SOH percentage between 85% and 95%</t>
-  </si>
-  <si>
-    <t>Battery Capacity at least 10%</t>
-  </si>
-  <si>
-    <t>Overall status bus plan</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>KPI</t>
-  </si>
-  <si>
-    <t>KPI-value</t>
-  </si>
-  <si>
-    <t>total_energy_kwh</t>
-  </si>
-  <si>
-    <t>total_distance_m</t>
-  </si>
-  <si>
-    <t>total_distance_km</t>
-  </si>
-  <si>
-    <t>deployed_buses_count</t>
-  </si>
-  <si>
-    <t>total_material_trips</t>
-  </si>
-  <si>
-    <t>total_waiting_time_min</t>
-  </si>
-  <si>
-    <t>total_waiting_time_hours</t>
-  </si>
-  <si>
-    <t>avg_waiting_time_per_bus_min</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -127,26 +46,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -434,121 +421,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="134.109375" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Location of end of trip and new trip match</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No Bus Overlap</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Required Trips of lines 400 and 401 included in bus plan</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Charging Duration is at least 15 min</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Number of Charging Speeds is equal to 2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>106</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>0</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Assumed SOH percentage between 85% and 95%</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Battery Capacity at least 10%</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Overall status bus plan</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>130</v>
       </c>
-      <c r="C10" t="s">
-        <v>14</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -557,82 +587,103 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="30.109375" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
-        <v>6537.5404000000044</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>KPI-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total_energy_kwh</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6537.540400000004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>total_distance_m</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>3533117</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>3533.1170000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total_distance_km</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3533.117</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>deployed_buses_count</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>20</v>
       </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_material_trips</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>total_waiting_time_min</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>775</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_waiting_time_hours</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>12.91666666666667</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>avg_waiting_time_per_bus_min</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>38.75</v>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,38 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_717342334DBFB53224E02F9F507F8525CE54304B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13107E9E-61C8-4AA7-9CFD-E0E656E0B973}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
+    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Errors</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Location of end of trip and new trip match</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>No Bus Overlap</t>
+  </si>
+  <si>
+    <t>Required Trips of lines 400 and 401 included in bus plan</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Charging Duration is at least 15 min</t>
+  </si>
+  <si>
+    <t>Number of Charging Speeds is equal to 2</t>
+  </si>
+  <si>
+    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
+  </si>
+  <si>
+    <t>Assumed SOH percentage between 85% and 95%</t>
+  </si>
+  <si>
+    <t>Battery Capacity at least 10%</t>
+  </si>
+  <si>
+    <t>Overall status bus plan</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>KPI-value</t>
+  </si>
+  <si>
+    <t>total_energy_kwh</t>
+  </si>
+  <si>
+    <t>total_distance_m</t>
+  </si>
+  <si>
+    <t>total_distance_km</t>
+  </si>
+  <si>
+    <t>deployed_buses_count</t>
+  </si>
+  <si>
+    <t>total_material_trips</t>
+  </si>
+  <si>
+    <t>total_waiting_time_min</t>
+  </si>
+  <si>
+    <t>total_waiting_time_hours</t>
+  </si>
+  <si>
+    <t>avg_waiting_time_per_bus_min</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,93 +134,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -421,164 +458,121 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="112.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Location of end of trip and new trip match</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
         <v>18</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>No Bus Overlap</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Required Trips of lines 400 and 401 included in bus plan</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Charging Duration is at least 15 min</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
         <v>106</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Number of Charging Speeds is equal to 2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Assumed SOH percentage between 85% and 95%</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Battery Capacity at least 10%</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
         <v>0</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Overall status bus plan</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
         <v>130</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
+      <c r="C10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -587,103 +581,82 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>KPI-value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>total_energy_kwh</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6537.540400000004</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>total_distance_m</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>6537.5404000000044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>3533117</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>total_distance_km</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3533.117</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>deployed_buses_count</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>3533.1170000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>total_material_trips</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>251</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>total_waiting_time_min</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>775</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>total_waiting_time_hours</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
         <v>12.91666666666667</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>avg_waiting_time_per_bus_min</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>38.75</v>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,125 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_717342334DBFB53224E02F9F507F8525CE54304B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13107E9E-61C8-4AA7-9CFD-E0E656E0B973}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
-    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Errors</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Location of end of trip and new trip match</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>No Bus Overlap</t>
-  </si>
-  <si>
-    <t>Required Trips of lines 400 and 401 included in bus plan</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Charging Duration is at least 15 min</t>
-  </si>
-  <si>
-    <t>Number of Charging Speeds is equal to 2</t>
-  </si>
-  <si>
-    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
-  </si>
-  <si>
-    <t>Assumed SOH percentage between 85% and 95%</t>
-  </si>
-  <si>
-    <t>Battery Capacity at least 10%</t>
-  </si>
-  <si>
-    <t>Overall status bus plan</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>KPI</t>
-  </si>
-  <si>
-    <t>KPI-value</t>
-  </si>
-  <si>
-    <t>total_energy_kwh</t>
-  </si>
-  <si>
-    <t>total_distance_m</t>
-  </si>
-  <si>
-    <t>total_distance_km</t>
-  </si>
-  <si>
-    <t>deployed_buses_count</t>
-  </si>
-  <si>
-    <t>total_material_trips</t>
-  </si>
-  <si>
-    <t>total_waiting_time_min</t>
-  </si>
-  <si>
-    <t>total_waiting_time_hours</t>
-  </si>
-  <si>
-    <t>avg_waiting_time_per_bus_min</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -134,43 +47,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -458,121 +421,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="112.85546875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Location of end of trip and new trip match</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No Bus Overlap</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Required Trips of lines 400 and 401 included in bus plan</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Charging Duration is at least 15 min</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Number of Charging Speeds is equal to 2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>106</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>0</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Assumed SOH percentage between 85% and 95%</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Battery Capacity at least 10%</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Overall status bus plan</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>130</v>
       </c>
-      <c r="C10" t="s">
-        <v>14</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -581,82 +587,103 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
-        <v>6537.5404000000044</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>KPI-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total_energy_kwh</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6537.540400000004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>total_distance_m</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>3533117</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>3533.1170000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total_distance_km</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3533.117</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>deployed_buses_count</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>20</v>
       </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_material_trips</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>total_waiting_time_min</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>775</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_waiting_time_hours</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>12.91666666666667</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>avg_waiting_time_per_bus_min</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>38.75</v>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -498,11 +498,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -558,11 +558,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>31</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>775</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.91666666666667</v>
+        <v>8.416666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.75</v>
+        <v>25.25</v>
       </c>
     </row>
   </sheetData>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,38 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_717342334DBFB5E2A0CAB7313163AE27FD52304C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B82CC54-398A-4DFD-A066-D586022DA756}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
+    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Errors</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Location of end of trip and new trip match</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>No Bus Overlap</t>
+  </si>
+  <si>
+    <t>Required Trips of lines 400 and 401 included in bus plan</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Charging Duration is at least 15 min</t>
+  </si>
+  <si>
+    <t>Number of Charging Speeds is equal to 2</t>
+  </si>
+  <si>
+    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
+  </si>
+  <si>
+    <t>Assumed SOH percentage between 85% and 95%</t>
+  </si>
+  <si>
+    <t>Battery Capacity at least 10%</t>
+  </si>
+  <si>
+    <t>Overall status bus plan</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>KPI-value</t>
+  </si>
+  <si>
+    <t>total_energy_kwh</t>
+  </si>
+  <si>
+    <t>total_distance_m</t>
+  </si>
+  <si>
+    <t>total_distance_km</t>
+  </si>
+  <si>
+    <t>deployed_buses_count</t>
+  </si>
+  <si>
+    <t>total_material_trips</t>
+  </si>
+  <si>
+    <t>total_waiting_time_min</t>
+  </si>
+  <si>
+    <t>total_waiting_time_hours</t>
+  </si>
+  <si>
+    <t>avg_waiting_time_per_bus_min</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,93 +134,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -421,164 +458,121 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="112.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Location of end of trip and new trip match</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
         <v>18</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>No Bus Overlap</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Required Trips of lines 400 and 401 included in bus plan</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Charging Duration is at least 15 min</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Number of Charging Speeds is equal to 2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Assumed SOH percentage between 85% and 95%</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Battery Capacity at least 10%</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="C8" t="s">
         <v>7</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Overall status bus plan</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
         <v>31</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
+      <c r="C10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -587,103 +581,79 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>KPI-value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>total_energy_kwh</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6537.540400000004</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>total_distance_m</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>6537.5404000000044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>3533117</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>total_distance_km</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3533.117</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>deployed_buses_count</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>3533.1170000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>total_material_trips</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>251</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>total_waiting_time_min</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>505</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>total_waiting_time_hours</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>8.416666666666666</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>avg_waiting_time_per_bus_min</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
+        <v>8.4166666666666661</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>25.25</v>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,125 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_717342334DBFB5E2A0CAB7313163AE27FD52304C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B82CC54-398A-4DFD-A066-D586022DA756}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
-    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Errors</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Location of end of trip and new trip match</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>No Bus Overlap</t>
-  </si>
-  <si>
-    <t>Required Trips of lines 400 and 401 included in bus plan</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Charging Duration is at least 15 min</t>
-  </si>
-  <si>
-    <t>Number of Charging Speeds is equal to 2</t>
-  </si>
-  <si>
-    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
-  </si>
-  <si>
-    <t>Assumed SOH percentage between 85% and 95%</t>
-  </si>
-  <si>
-    <t>Battery Capacity at least 10%</t>
-  </si>
-  <si>
-    <t>Overall status bus plan</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>KPI</t>
-  </si>
-  <si>
-    <t>KPI-value</t>
-  </si>
-  <si>
-    <t>total_energy_kwh</t>
-  </si>
-  <si>
-    <t>total_distance_m</t>
-  </si>
-  <si>
-    <t>total_distance_km</t>
-  </si>
-  <si>
-    <t>deployed_buses_count</t>
-  </si>
-  <si>
-    <t>total_material_trips</t>
-  </si>
-  <si>
-    <t>total_waiting_time_min</t>
-  </si>
-  <si>
-    <t>total_waiting_time_hours</t>
-  </si>
-  <si>
-    <t>avg_waiting_time_per_bus_min</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -134,43 +47,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -458,121 +421,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="112.85546875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Location of end of trip and new trip match</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No Bus Overlap</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Required Trips of lines 400 and 401 included in bus plan</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Charging Duration is at least 15 min</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>106</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Number of Charging Speeds is equal to 2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>0</v>
       </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Assumed SOH percentage between 85% and 95%</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>0</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Battery Capacity at least 10%</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Overall status bus plan</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>130</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -581,80 +587,104 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
-        <v>6537.5404000000044</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>3533117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>3533.1170000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>KPI-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total_energy_kwh</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6537.540400000004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>total_distance_m</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4952117</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total_distance_km</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4952.117</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>deployed_buses_count</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>20</v>
       </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_material_trips</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
-        <v>8.4166666666666661</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <v>25.25</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>total_waiting_time_min</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_waiting_time_hours</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12.91666666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>avg_waiting_time_per_bus_min</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>38.75</v>
       </c>
     </row>
   </sheetData>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,38 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1942B172-7D6F-4A09-B182-808FBA510D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
+    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Errors</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Location of end of trip and new trip match</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>No Bus Overlap</t>
+  </si>
+  <si>
+    <t>Required Trips of lines 400 and 401 included in bus plan</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Charging Duration is at least 15 min</t>
+  </si>
+  <si>
+    <t>Number of Charging Speeds is equal to 2</t>
+  </si>
+  <si>
+    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
+  </si>
+  <si>
+    <t>Assumed SOH percentage between 85% and 95%</t>
+  </si>
+  <si>
+    <t>Battery Capacity at least 10%</t>
+  </si>
+  <si>
+    <t>Overall status bus plan</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>KPI-value</t>
+  </si>
+  <si>
+    <t>total_energy_kwh</t>
+  </si>
+  <si>
+    <t>total_distance_m</t>
+  </si>
+  <si>
+    <t>total_distance_km</t>
+  </si>
+  <si>
+    <t>deployed_buses_count</t>
+  </si>
+  <si>
+    <t>total_material_trips</t>
+  </si>
+  <si>
+    <t>total_waiting_time_min</t>
+  </si>
+  <si>
+    <t>total_waiting_time_hours</t>
+  </si>
+  <si>
+    <t>avg_waiting_time_per_bus_min</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,93 +134,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -421,164 +458,122 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="103.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Location of end of trip and new trip match</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
         <v>18</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>No Bus Overlap</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Required Trips of lines 400 and 401 included in bus plan</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Charging Duration is at least 15 min</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
         <v>106</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Number of Charging Speeds is equal to 2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Assumed SOH percentage between 85% and 95%</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Battery Capacity at least 10%</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
         <v>0</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Overall status bus plan</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
         <v>130</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
+      <c r="C10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -587,103 +582,83 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>KPI-value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>total_energy_kwh</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6537.540400000004</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>total_distance_m</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>6537.5404000000044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>4952117</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>total_distance_km</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4952.117</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>deployed_buses_count</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>4952.1170000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>total_material_trips</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>251</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>total_waiting_time_min</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>775</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>total_waiting_time_hours</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
         <v>12.91666666666667</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>avg_waiting_time_per_bus_min</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>38.75</v>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,125 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1942B172-7D6F-4A09-B182-808FBA510D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
-    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Errors</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Location of end of trip and new trip match</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>No Bus Overlap</t>
-  </si>
-  <si>
-    <t>Required Trips of lines 400 and 401 included in bus plan</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Charging Duration is at least 15 min</t>
-  </si>
-  <si>
-    <t>Number of Charging Speeds is equal to 2</t>
-  </si>
-  <si>
-    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
-  </si>
-  <si>
-    <t>Assumed SOH percentage between 85% and 95%</t>
-  </si>
-  <si>
-    <t>Battery Capacity at least 10%</t>
-  </si>
-  <si>
-    <t>Overall status bus plan</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>KPI</t>
-  </si>
-  <si>
-    <t>KPI-value</t>
-  </si>
-  <si>
-    <t>total_energy_kwh</t>
-  </si>
-  <si>
-    <t>total_distance_m</t>
-  </si>
-  <si>
-    <t>total_distance_km</t>
-  </si>
-  <si>
-    <t>deployed_buses_count</t>
-  </si>
-  <si>
-    <t>total_material_trips</t>
-  </si>
-  <si>
-    <t>total_waiting_time_min</t>
-  </si>
-  <si>
-    <t>total_waiting_time_hours</t>
-  </si>
-  <si>
-    <t>avg_waiting_time_per_bus_min</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -134,43 +47,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -458,122 +421,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="103.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Location of end of trip and new trip match</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No Bus Overlap</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Required Trips of lines 400 and 401 included in bus plan</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Charging Duration is at least 15 min</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Number of Charging Speeds is equal to 2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Assumed SOH percentage between 85% and 95%</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Battery Capacity at least 10%</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>106</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
-        <v>130</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Overall status bus plan</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>31</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -582,84 +587,104 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="31.44140625" customWidth="1"/>
-    <col min="2" max="2" width="24.21875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
-        <v>6537.5404000000044</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>4952117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>4952.1170000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>KPI-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>total_energy_kwh</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6537.540400000004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>total_distance_m</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3533117</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>total_distance_km</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3533.117</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>deployed_buses_count</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>20</v>
       </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_material_trips</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
-        <v>12.91666666666667</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <v>38.75</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>total_waiting_time_min</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_waiting_time_hours</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8.416666666666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>avg_waiting_time_per_bus_min</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>25.25</v>
       </c>
     </row>
   </sheetData>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,17 +418,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -498,11 +486,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -558,11 +546,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -573,7 +561,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -596,12 +584,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>KPI-value</t>
         </is>
@@ -664,7 +652,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>505</v>
+        <v>775</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +662,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.416666666666666</v>
+        <v>12.91666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -684,7 +672,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.25</v>
+        <v>38.75</v>
       </c>
     </row>
   </sheetData>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -486,11 +486,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,35 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baswe\Documents\GitHub\Project_5\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99EC198E-117B-4573-B04E-F12F263F438C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Feasibility_checks" sheetId="1" r:id="rId1"/>
+    <sheet name="KPI_values" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Errors</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Location of end of trip and new trip match</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>No Bus Overlap</t>
+  </si>
+  <si>
+    <t>Required Trips of lines 400 and 401 included in bus plan</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Charging Duration is at least 15 min</t>
+  </si>
+  <si>
+    <t>Number of Charging Speeds is equal to 2</t>
+  </si>
+  <si>
+    <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
+  </si>
+  <si>
+    <t>Assumed SOH percentage between 85% and 95%</t>
+  </si>
+  <si>
+    <t>Battery Capacity at least 10%</t>
+  </si>
+  <si>
+    <t>Overall status bus plan</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>KPI-value</t>
+  </si>
+  <si>
+    <t>total_energy_kwh</t>
+  </si>
+  <si>
+    <t>total_distance_m</t>
+  </si>
+  <si>
+    <t>total_distance_km</t>
+  </si>
+  <si>
+    <t>deployed_buses_count</t>
+  </si>
+  <si>
+    <t>total_material_trips</t>
+  </si>
+  <si>
+    <t>total_waiting_time_min</t>
+  </si>
+  <si>
+    <t>total_waiting_time_hours</t>
+  </si>
+  <si>
+    <t>avg_waiting_time_per_bus_min</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,80 +132,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,164 +434,121 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="71.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Errors</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Location of end of trip and new trip match</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
         <v>18</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>No Bus Overlap</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Required Trips of lines 400 and 401 included in bus plan</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Charging Duration is at least 15 min</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Number of Charging Speeds is equal to 2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Charging speeds configured (Quick (0-90% battery capacity): 7.50 kWh/min, Slow (90-100% battery capacity): 1.00 kWh/min)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Assumed SOH percentage between 85% and 95%</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Battery Capacity at least 10%</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
         <v>0</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Overall status bus plan</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
         <v>24</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
+      <c r="C10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -575,103 +557,79 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>KPI-value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>total_energy_kwh</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6537.540400000004</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>total_distance_m</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>6537.5404000000044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
         <v>3533117</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>total_distance_km</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3533.117</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>deployed_buses_count</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>3533.1170000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>total_material_trips</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>251</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>total_waiting_time_min</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
         <v>775</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>total_waiting_time_hours</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
         <v>12.91666666666667</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>avg_waiting_time_per_bus_min</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>38.75</v>
       </c>
     </row>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -498,11 +498,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -558,11 +558,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3533117</v>
+        <v>4952117</v>
       </c>
     </row>
     <row r="4">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3533.117</v>
+        <v>4952.117</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>505</v>
+        <v>775</v>
       </c>
     </row>
     <row r="8">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.416666666666666</v>
+        <v>12.91666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.25</v>
+        <v>38.75</v>
       </c>
     </row>
   </sheetData>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,17 +418,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -596,12 +584,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>KPI-value</t>
         </is>

--- a/Feasibility_and_KPI_results_busplan.xlsx
+++ b/Feasibility_and_KPI_results_busplan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feasibility_checks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI_values" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,17 +430,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -584,12 +596,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>KPI-value</t>
         </is>
